--- a/Output/summary_OMOP_vocabs_merge.xlsx
+++ b/Output/summary_OMOP_vocabs_merge.xlsx
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="B5">
-        <v>439777</v>
+        <v>4113639</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -594,7 +594,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Anemia</t>
+          <t>Benign genital neoplasm</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -619,7 +619,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>271737000</t>
+          <t>286904004</t>
         </is>
       </c>
       <c r="J5" s="2">
@@ -682,7 +682,7 @@
         </is>
       </c>
       <c r="B7">
-        <v>376106</v>
+        <v>36210384</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -691,22 +691,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Disorder of the central nervous system</t>
+          <t>Stroke</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Condition</t>
+          <t>Meas Value</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>SNOMED</t>
+          <t>LOINC</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Disorder</t>
+          <t>Answer</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -716,11 +716,11 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>23853001</t>
+          <t>LA22099-8</t>
         </is>
       </c>
       <c r="J7" s="2">
-        <v>37287</v>
+        <v>25569</v>
       </c>
       <c r="K7" s="2">
         <v>73050</v>
@@ -733,7 +733,7 @@
         </is>
       </c>
       <c r="B8">
-        <v>36210384</v>
+        <v>439727</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -742,22 +742,22 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Stroke</t>
+          <t>Human immunodeficiency virus infection</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Meas Value</t>
+          <t>Condition</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>LOINC</t>
+          <t>SNOMED</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Answer</t>
+          <t>Disorder</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -767,11 +767,11 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>LA22099-8</t>
+          <t>86406008</t>
         </is>
       </c>
       <c r="J8" s="2">
-        <v>25569</v>
+        <v>37287</v>
       </c>
       <c r="K8" s="2">
         <v>73050</v>
@@ -784,7 +784,7 @@
         </is>
       </c>
       <c r="B9">
-        <v>441413</v>
+        <v>432250</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -793,12 +793,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Death of unknown cause</t>
+          <t>Infectious disease</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Observation</t>
+          <t>Condition</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>Disorder</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -818,7 +818,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>87309006</t>
+          <t>40733004</t>
         </is>
       </c>
       <c r="J9" s="2">
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="B10">
-        <v>4134607</v>
+        <v>321588</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Diarrheal disorder</t>
+          <t>Heart disease</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>128333008</t>
+          <t>56265001</t>
         </is>
       </c>
       <c r="J10" s="2">
@@ -886,7 +886,7 @@
         </is>
       </c>
       <c r="B11">
-        <v>40759950</v>
+        <v>196931</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -895,22 +895,22 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Problem associated signs and symptoms</t>
+          <t>Neoplasm of digestive tract</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Observation</t>
+          <t>Condition</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>LOINC</t>
+          <t>SNOMED</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Clinical Observation</t>
+          <t>Disorder</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -920,11 +920,11 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>56831-1</t>
+          <t>128415001</t>
         </is>
       </c>
       <c r="J11" s="2">
-        <v>40042</v>
+        <v>37287</v>
       </c>
       <c r="K11" s="2">
         <v>73050</v>
@@ -937,7 +937,7 @@
         </is>
       </c>
       <c r="B12">
-        <v>4347554</v>
+        <v>4112341</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Viral hemorrhagic fever</t>
+          <t>Acute respiratory infections</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>240523007</t>
+          <t>195647007</t>
         </is>
       </c>
       <c r="J12" s="2">
@@ -988,7 +988,7 @@
         </is>
       </c>
       <c r="B13">
-        <v>4113639</v>
+        <v>192359</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Benign genital neoplasm</t>
+          <t>Renal failure syndrome</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>286904004</t>
+          <t>42399005</t>
         </is>
       </c>
       <c r="J13" s="2">
@@ -1039,7 +1039,7 @@
         </is>
       </c>
       <c r="B14">
-        <v>255848</v>
+        <v>440370</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Pneumonia</t>
+          <t>Nutritional marasmus</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>233604007</t>
+          <t>29740003</t>
         </is>
       </c>
       <c r="J14" s="2">
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="B15">
-        <v>4112341</v>
+        <v>4064161</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Acute respiratory infections</t>
+          <t>Cirrhosis of liver</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>195647007</t>
+          <t>19943007</t>
         </is>
       </c>
       <c r="J15" s="2">
@@ -1141,7 +1141,7 @@
         </is>
       </c>
       <c r="B16">
-        <v>380378</v>
+        <v>443783</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Epilepsy</t>
+          <t>Chronic disease</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>84757009</t>
+          <t>27624003</t>
         </is>
       </c>
       <c r="J16" s="2">
@@ -1192,7 +1192,7 @@
         </is>
       </c>
       <c r="B17">
-        <v>316866</v>
+        <v>444066</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Hypertensive disorder</t>
+          <t>Rupture of uterus</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>38341003</t>
+          <t>34430009</t>
         </is>
       </c>
       <c r="J17" s="2">
@@ -1243,7 +1243,7 @@
         </is>
       </c>
       <c r="B18">
-        <v>4053720</v>
+        <v>201820</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Accidental injury</t>
+          <t>Diabetes mellitus</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1277,7 +1277,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>242056005</t>
+          <t>73211009</t>
         </is>
       </c>
       <c r="J18" s="2">
@@ -1294,7 +1294,7 @@
         </is>
       </c>
       <c r="B19">
-        <v>201820</v>
+        <v>253954</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Diabetes mellitus</t>
+          <t>Pulmonary tuberculosis</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1328,11 +1328,11 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>73211009</t>
+          <t>154283005</t>
         </is>
       </c>
       <c r="J19" s="2">
-        <v>37287</v>
+        <v>37833</v>
       </c>
       <c r="K19" s="2">
         <v>73050</v>
@@ -1345,7 +1345,7 @@
         </is>
       </c>
       <c r="B20">
-        <v>196931</v>
+        <v>432582</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Neoplasm of digestive tract</t>
+          <t>Neoplastic disease of uncertain behavior</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>128415001</t>
+          <t>118616009</t>
         </is>
       </c>
       <c r="J20" s="2">
@@ -1396,7 +1396,7 @@
         </is>
       </c>
       <c r="B21">
-        <v>4064161</v>
+        <v>4134607</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Cirrhosis of liver</t>
+          <t>Diarrheal disorder</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>19943007</t>
+          <t>128333008</t>
         </is>
       </c>
       <c r="J21" s="2">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="B22">
-        <v>4023573</v>
+        <v>437165</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -1456,12 +1456,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Acute abdominal pain</t>
+          <t>Motor vehicle traffic accident</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Condition</t>
+          <t>Observation</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Clinical Finding</t>
+          <t>Event</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>116290004</t>
+          <t>214031005</t>
         </is>
       </c>
       <c r="J22" s="2">
@@ -1498,7 +1498,7 @@
         </is>
       </c>
       <c r="B23">
-        <v>440370</v>
+        <v>4241033</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -1507,7 +1507,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Nutritional marasmus</t>
+          <t>Acute abdomen</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>29740003</t>
+          <t>9209005</t>
         </is>
       </c>
       <c r="J23" s="2">
@@ -1549,7 +1549,7 @@
         </is>
       </c>
       <c r="B24">
-        <v>439727</v>
+        <v>432795</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -1558,7 +1558,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Human immunodeficiency virus infection</t>
+          <t>Traumatic or non-traumatic injury</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1583,11 +1583,11 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>86406008</t>
+          <t>417163006</t>
         </is>
       </c>
       <c r="J24" s="2">
-        <v>37287</v>
+        <v>38564</v>
       </c>
       <c r="K24" s="2">
         <v>73050</v>
@@ -1600,7 +1600,7 @@
         </is>
       </c>
       <c r="B25">
-        <v>317009</v>
+        <v>438067</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Asthma</t>
+          <t>Malaria</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>195967001</t>
+          <t>61462000</t>
         </is>
       </c>
       <c r="J25" s="2">
@@ -1651,7 +1651,7 @@
         </is>
       </c>
       <c r="B26">
-        <v>198124</v>
+        <v>252280</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Kidney disease</t>
+          <t>Neoplasm of respiratory tract</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1685,7 +1685,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>90708001</t>
+          <t>126667002</t>
         </is>
       </c>
       <c r="J26" s="2">
@@ -1702,7 +1702,7 @@
         </is>
       </c>
       <c r="B27">
-        <v>4034159</v>
+        <v>4303690</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -1711,12 +1711,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Fresh stillbirth</t>
+          <t>Intentionally harming self</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Condition</t>
+          <t>Observation</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1726,7 +1726,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Clinical Finding</t>
+          <t>Event</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>237365001</t>
+          <t>418420002</t>
         </is>
       </c>
       <c r="J27" s="2">
-        <v>37287</v>
+        <v>38748</v>
       </c>
       <c r="K27" s="2">
         <v>73050</v>
@@ -1753,7 +1753,7 @@
         </is>
       </c>
       <c r="B28">
-        <v>432795</v>
+        <v>439237</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Traumatic or non-traumatic injury</t>
+          <t>Assault</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Condition</t>
+          <t>Observation</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1777,7 +1777,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Disorder</t>
+          <t>Event</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1787,11 +1787,11 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>417163006</t>
+          <t>52684005</t>
         </is>
       </c>
       <c r="J28" s="2">
-        <v>38564</v>
+        <v>37287</v>
       </c>
       <c r="K28" s="2">
         <v>73050</v>
@@ -1804,7 +1804,7 @@
         </is>
       </c>
       <c r="B29">
-        <v>4042220</v>
+        <v>4155221</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1813,12 +1813,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Neonatal disorder</t>
+          <t>Exposure to poison of venomous animals and plants</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Condition</t>
+          <t>Observation</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1828,7 +1828,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Disorder</t>
+          <t>Event</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>22925008</t>
+          <t>269705003</t>
         </is>
       </c>
       <c r="J29" s="2">
@@ -1855,7 +1855,7 @@
         </is>
       </c>
       <c r="B30">
-        <v>196151</v>
+        <v>4347554</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1864,7 +1864,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Functional disorder of intestine</t>
+          <t>Viral hemorrhagic fever</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>81120009</t>
+          <t>240523007</t>
         </is>
       </c>
       <c r="J30" s="2">
@@ -1906,7 +1906,7 @@
         </is>
       </c>
       <c r="B31">
-        <v>26942</v>
+        <v>4322814</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Hemoglobin SS disease with crisis</t>
+          <t>Meningoencephalitis</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1940,11 +1940,11 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>417425009</t>
+          <t>7125002</t>
         </is>
       </c>
       <c r="J31" s="2">
-        <v>38564</v>
+        <v>37287</v>
       </c>
       <c r="K31" s="2">
         <v>73050</v>
@@ -1957,7 +1957,7 @@
         </is>
       </c>
       <c r="B32">
-        <v>4079975</v>
+        <v>4215140</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Congenital malformation</t>
+          <t>Acute coronary syndrome</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1991,11 +1991,11 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>276654001</t>
+          <t>394659003</t>
         </is>
       </c>
       <c r="J32" s="2">
-        <v>37287</v>
+        <v>37652</v>
       </c>
       <c r="K32" s="2">
         <v>73050</v>
@@ -2008,7 +2008,7 @@
         </is>
       </c>
       <c r="B33">
-        <v>443700</v>
+        <v>132797</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -2017,7 +2017,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Eclampsia</t>
+          <t>Sepsis</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2042,7 +2042,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>15938005</t>
+          <t>91302008</t>
         </is>
       </c>
       <c r="J33" s="2">
@@ -2059,7 +2059,7 @@
         </is>
       </c>
       <c r="B34">
-        <v>439658</v>
+        <v>81251</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -2068,7 +2068,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Disorder of pregnancy</t>
+          <t>Neoplasm of breast</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2093,7 +2093,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>173300003</t>
+          <t>126926005</t>
         </is>
       </c>
       <c r="J34" s="2">
@@ -2110,7 +2110,7 @@
         </is>
       </c>
       <c r="B35">
-        <v>443929</v>
+        <v>380378</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -2119,7 +2119,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Postpartum hemorrhage</t>
+          <t>Epilepsy</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2144,7 +2144,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>47821001</t>
+          <t>84757009</t>
         </is>
       </c>
       <c r="J35" s="2">
@@ -2161,7 +2161,7 @@
         </is>
       </c>
       <c r="B36">
-        <v>437165</v>
+        <v>4080913</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -2170,12 +2170,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Motor vehicle traffic accident</t>
+          <t>Amputation-related dermatosis</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Observation</t>
+          <t>Condition</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2185,7 +2185,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>Disorder</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>214031005</t>
+          <t>238488003</t>
         </is>
       </c>
       <c r="J36" s="2">
@@ -2212,7 +2212,7 @@
         </is>
       </c>
       <c r="B37">
-        <v>4215140</v>
+        <v>443929</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Acute coronary syndrome</t>
+          <t>Postpartum hemorrhage</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2246,11 +2246,11 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>394659003</t>
+          <t>47821001</t>
         </is>
       </c>
       <c r="J37" s="2">
-        <v>37652</v>
+        <v>37287</v>
       </c>
       <c r="K37" s="2">
         <v>73050</v>
@@ -2263,7 +2263,7 @@
         </is>
       </c>
       <c r="B38">
-        <v>36675035</v>
+        <v>435991</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -2272,12 +2272,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Prematurity of infant</t>
+          <t>Accidental fall</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Condition</t>
+          <t>Observation</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2287,7 +2287,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Disorder</t>
+          <t>Event</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2297,11 +2297,11 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>771299009</t>
+          <t>217082002</t>
         </is>
       </c>
       <c r="J38" s="2">
-        <v>43496</v>
+        <v>37287</v>
       </c>
       <c r="K38" s="2">
         <v>73050</v>
@@ -2314,7 +2314,7 @@
         </is>
       </c>
       <c r="B39">
-        <v>435740</v>
+        <v>255573</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -2323,7 +2323,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Tetanus</t>
+          <t>Chronic obstructive pulmonary disease</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2348,7 +2348,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>76902006</t>
+          <t>13645005</t>
         </is>
       </c>
       <c r="J39" s="2">
@@ -2365,7 +2365,7 @@
         </is>
       </c>
       <c r="B40">
-        <v>4310575</v>
+        <v>436593</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -2374,12 +2374,12 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Carcinoma of uterine cervix, invasive</t>
+          <t>Accidental drowning and submersion</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Condition</t>
+          <t>Observation</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2389,7 +2389,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Disorder</t>
+          <t>Event</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2399,11 +2399,11 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>423973006</t>
+          <t>217748000</t>
         </is>
       </c>
       <c r="J40" s="2">
-        <v>39113</v>
+        <v>37287</v>
       </c>
       <c r="K40" s="2">
         <v>73050</v>
@@ -2416,7 +2416,7 @@
         </is>
       </c>
       <c r="B41">
-        <v>253954</v>
+        <v>436581</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -2425,7 +2425,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Pulmonary tuberculosis</t>
+          <t>Accidental poisoning</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2450,11 +2450,11 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>154283005</t>
+          <t>72431002</t>
         </is>
       </c>
       <c r="J41" s="2">
-        <v>37833</v>
+        <v>37287</v>
       </c>
       <c r="K41" s="2">
         <v>73050</v>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="B42">
-        <v>252280</v>
+        <v>317009</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -2476,7 +2476,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Neoplasm of respiratory tract</t>
+          <t>Asthma</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>126667002</t>
+          <t>195967001</t>
         </is>
       </c>
       <c r="J42" s="2">
@@ -2518,7 +2518,7 @@
         </is>
       </c>
       <c r="B43">
-        <v>4184996</v>
+        <v>439777</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Birth asphyxia</t>
+          <t>Anemia</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2552,11 +2552,11 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>413654009</t>
+          <t>271737000</t>
         </is>
       </c>
       <c r="J43" s="2">
-        <v>38383</v>
+        <v>37287</v>
       </c>
       <c r="K43" s="2">
         <v>73050</v>
@@ -2569,7 +2569,7 @@
         </is>
       </c>
       <c r="B44">
-        <v>4241033</v>
+        <v>4099889</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Acute abdomen</t>
+          <t>Anemia of pregnancy</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>9209005</t>
+          <t>27342004</t>
         </is>
       </c>
       <c r="J44" s="2">
@@ -2620,7 +2620,7 @@
         </is>
       </c>
       <c r="B45">
-        <v>438067</v>
+        <v>4130986</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -2629,7 +2629,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Malaria</t>
+          <t>Neoplasm of mouth</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2654,7 +2654,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>61462000</t>
+          <t>126797001</t>
         </is>
       </c>
       <c r="J45" s="2">
@@ -2671,7 +2671,7 @@
         </is>
       </c>
       <c r="B46">
-        <v>381591</v>
+        <v>440022</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Cerebrovascular disease</t>
+          <t>Dengue</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2705,7 +2705,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>62914000</t>
+          <t>38362002</t>
         </is>
       </c>
       <c r="J46" s="2">
@@ -2722,7 +2722,7 @@
         </is>
       </c>
       <c r="B47">
-        <v>4051337</v>
+        <v>437453</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -2731,12 +2731,12 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Neonatal pneumonia</t>
+          <t>Accident due to environmental factor</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Condition</t>
+          <t>Observation</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Disorder</t>
+          <t>Event</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2756,7 +2756,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>233619008</t>
+          <t>217591008</t>
         </is>
       </c>
       <c r="J47" s="2">
@@ -2773,7 +2773,7 @@
         </is>
       </c>
       <c r="B48">
-        <v>436581</v>
+        <v>37175321</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Accidental poisoning</t>
+          <t>Antepartum septicemia</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2807,11 +2807,11 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>72431002</t>
+          <t>137701000119106</t>
         </is>
       </c>
       <c r="J48" s="2">
-        <v>37287</v>
+        <v>45107</v>
       </c>
       <c r="K48" s="2">
         <v>73050</v>
@@ -2824,7 +2824,7 @@
         </is>
       </c>
       <c r="B49">
-        <v>4116071</v>
+        <v>435740</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Carcinoma of breast</t>
+          <t>Tetanus</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2858,7 +2858,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>254838004</t>
+          <t>76902006</t>
         </is>
       </c>
       <c r="J49" s="2">
@@ -2875,7 +2875,7 @@
         </is>
       </c>
       <c r="B50">
-        <v>4322814</v>
+        <v>4167493</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Meningoencephalitis</t>
+          <t>Pregnancy-induced hypertension</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>7125002</t>
+          <t>48194001</t>
         </is>
       </c>
       <c r="J50" s="2">
@@ -2926,7 +2926,7 @@
         </is>
       </c>
       <c r="B51">
-        <v>432582</v>
+        <v>4051337</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -2935,7 +2935,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Neoplastic disease of uncertain behavior</t>
+          <t>Neonatal pneumonia</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -2960,7 +2960,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>118616009</t>
+          <t>233619008</t>
         </is>
       </c>
       <c r="J51" s="2">
@@ -2977,7 +2977,7 @@
         </is>
       </c>
       <c r="B52">
-        <v>435991</v>
+        <v>4184996</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -2986,12 +2986,12 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Accidental fall</t>
+          <t>Birth asphyxia</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Observation</t>
+          <t>Condition</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -3001,7 +3001,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>Disorder</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3011,11 +3011,11 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>217082002</t>
+          <t>413654009</t>
         </is>
       </c>
       <c r="J52" s="2">
-        <v>37287</v>
+        <v>38383</v>
       </c>
       <c r="K52" s="2">
         <v>73050</v>
@@ -3028,7 +3028,7 @@
         </is>
       </c>
       <c r="B53">
-        <v>4303690</v>
+        <v>36675035</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -3037,12 +3037,12 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Intentionally harming self</t>
+          <t>Prematurity of infant</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Observation</t>
+          <t>Condition</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -3052,7 +3052,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>Disorder</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3062,11 +3062,11 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>418420002</t>
+          <t>771299009</t>
         </is>
       </c>
       <c r="J53" s="2">
-        <v>38748</v>
+        <v>43496</v>
       </c>
       <c r="K53" s="2">
         <v>73050</v>
@@ -3079,7 +3079,7 @@
         </is>
       </c>
       <c r="B54">
-        <v>132797</v>
+        <v>4071063</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -3088,7 +3088,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Sepsis</t>
+          <t>Sepsis of the newborn</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3113,7 +3113,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>91302008</t>
+          <t>206376005</t>
         </is>
       </c>
       <c r="J54" s="2">
@@ -3130,7 +3130,7 @@
         </is>
       </c>
       <c r="B55">
-        <v>435656</v>
+        <v>4042220</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -3139,7 +3139,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Neonatal jaundice</t>
+          <t>Neonatal disorder</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Clinical Finding</t>
+          <t>Disorder</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3164,11 +3164,11 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>387712008</t>
+          <t>22925008</t>
         </is>
       </c>
       <c r="J55" s="2">
-        <v>37652</v>
+        <v>37287</v>
       </c>
       <c r="K55" s="2">
         <v>73050</v>
@@ -3181,7 +3181,7 @@
         </is>
       </c>
       <c r="B56">
-        <v>4244495</v>
+        <v>26942</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -3190,7 +3190,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Carcinoma in situ of gastrointestinal tract</t>
+          <t>Hemoglobin SS disease with crisis</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3215,11 +3215,11 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>92600008</t>
+          <t>417425009</t>
         </is>
       </c>
       <c r="J56" s="2">
-        <v>37287</v>
+        <v>38564</v>
       </c>
       <c r="K56" s="2">
         <v>73050</v>
@@ -3232,7 +3232,7 @@
         </is>
       </c>
       <c r="B57">
-        <v>442013</v>
+        <v>4143700</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Burn</t>
+          <t>Smoke inhalation injury</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3266,11 +3266,11 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>125666000</t>
+          <t>426936004</t>
         </is>
       </c>
       <c r="J57" s="2">
-        <v>37287</v>
+        <v>39294</v>
       </c>
       <c r="K57" s="2">
         <v>73050</v>
@@ -3283,7 +3283,7 @@
         </is>
       </c>
       <c r="B58">
-        <v>432250</v>
+        <v>4079975</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -3292,7 +3292,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Infectious disease</t>
+          <t>Congenital malformation</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3317,7 +3317,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>40733004</t>
+          <t>276654001</t>
         </is>
       </c>
       <c r="J58" s="2">
@@ -3334,7 +3334,7 @@
         </is>
       </c>
       <c r="B59">
-        <v>4167493</v>
+        <v>376106</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -3343,7 +3343,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Pregnancy-induced hypertension</t>
+          <t>Disorder of the central nervous system</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -3368,7 +3368,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>48194001</t>
+          <t>23853001</t>
         </is>
       </c>
       <c r="J59" s="2">
@@ -3385,7 +3385,7 @@
         </is>
       </c>
       <c r="B60">
-        <v>40492938</v>
+        <v>441413</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -3394,12 +3394,12 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Carcinoma of lung</t>
+          <t>Death of unknown cause</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Condition</t>
+          <t>Observation</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -3409,7 +3409,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Disorder</t>
+          <t>Event</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -3419,11 +3419,11 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>448993007</t>
+          <t>87309006</t>
         </is>
       </c>
       <c r="J60" s="2">
-        <v>40755</v>
+        <v>37287</v>
       </c>
       <c r="K60" s="2">
         <v>73050</v>
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="B61">
-        <v>4291005</v>
+        <v>40759950</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -3445,22 +3445,22 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Viral hepatitis</t>
+          <t>Problem associated signs and symptoms</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Condition</t>
+          <t>Observation</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>SNOMED</t>
+          <t>LOINC</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Disorder</t>
+          <t>Clinical Observation</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -3470,11 +3470,11 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>3738000</t>
+          <t>56831-1</t>
         </is>
       </c>
       <c r="J61" s="2">
-        <v>37287</v>
+        <v>40042</v>
       </c>
       <c r="K61" s="2">
         <v>73050</v>
@@ -3487,7 +3487,7 @@
         </is>
       </c>
       <c r="B62">
-        <v>133024</v>
+        <v>255848</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -3496,7 +3496,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Tetanus neonatorum</t>
+          <t>Pneumonia</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -3521,7 +3521,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>43424001</t>
+          <t>233604007</t>
         </is>
       </c>
       <c r="J62" s="2">
@@ -3538,7 +3538,7 @@
         </is>
       </c>
       <c r="B63">
-        <v>436593</v>
+        <v>316866</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -3547,12 +3547,12 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Accidental drowning and submersion</t>
+          <t>Hypertensive disorder</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Observation</t>
+          <t>Condition</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -3562,7 +3562,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>Disorder</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -3572,7 +3572,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>217748000</t>
+          <t>38341003</t>
         </is>
       </c>
       <c r="J63" s="2">
@@ -3589,7 +3589,7 @@
         </is>
       </c>
       <c r="B64">
-        <v>134057</v>
+        <v>4053720</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Disorder of cardiovascular system</t>
+          <t>Accidental injury</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -3623,7 +3623,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>49601007</t>
+          <t>242056005</t>
         </is>
       </c>
       <c r="J64" s="2">
@@ -3640,7 +3640,7 @@
         </is>
       </c>
       <c r="B65">
-        <v>4101415</v>
+        <v>4023573</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -3649,12 +3649,12 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Homicide</t>
+          <t>Acute abdominal pain</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Observation</t>
+          <t>Condition</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -3664,7 +3664,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>Clinical Finding</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>27935005</t>
+          <t>116290004</t>
         </is>
       </c>
       <c r="J65" s="2">
@@ -3691,7 +3691,7 @@
         </is>
       </c>
       <c r="B66">
-        <v>192359</v>
+        <v>198124</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -3700,7 +3700,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Renal failure syndrome</t>
+          <t>Kidney disease</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -3725,7 +3725,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>42399005</t>
+          <t>90708001</t>
         </is>
       </c>
       <c r="J66" s="2">
@@ -3742,7 +3742,7 @@
         </is>
       </c>
       <c r="B67">
-        <v>45877493</v>
+        <v>4034159</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -3751,22 +3751,22 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Animal bite</t>
+          <t>Fresh stillbirth</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Meas Value</t>
+          <t>Condition</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>LOINC</t>
+          <t>SNOMED</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Answer</t>
+          <t>Clinical Finding</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -3776,11 +3776,11 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>LA17118-3</t>
+          <t>237365001</t>
         </is>
       </c>
       <c r="J67" s="2">
-        <v>25569</v>
+        <v>37287</v>
       </c>
       <c r="K67" s="2">
         <v>73050</v>
@@ -3793,7 +3793,7 @@
         </is>
       </c>
       <c r="B68">
-        <v>321588</v>
+        <v>196151</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -3802,7 +3802,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Heart disease</t>
+          <t>Functional disorder of intestine</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -3827,7 +3827,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>56265001</t>
+          <t>81120009</t>
         </is>
       </c>
       <c r="J68" s="2">
@@ -3844,7 +3844,7 @@
         </is>
       </c>
       <c r="B69">
-        <v>4080913</v>
+        <v>443700</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -3853,7 +3853,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Amputation-related dermatosis</t>
+          <t>Eclampsia</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -3878,7 +3878,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>238488003</t>
+          <t>15938005</t>
         </is>
       </c>
       <c r="J69" s="2">
@@ -3895,7 +3895,7 @@
         </is>
       </c>
       <c r="B70">
-        <v>434557</v>
+        <v>439658</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -3904,7 +3904,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Tuberculosis</t>
+          <t>Disorder of pregnancy</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -3929,7 +3929,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>56717001</t>
+          <t>173300003</t>
         </is>
       </c>
       <c r="J70" s="2">
@@ -3946,7 +3946,7 @@
         </is>
       </c>
       <c r="B71">
-        <v>200763</v>
+        <v>4310575</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Chronic hepatitis</t>
+          <t>Carcinoma of uterine cervix, invasive</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -3980,11 +3980,11 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>76783007</t>
+          <t>423973006</t>
         </is>
       </c>
       <c r="J71" s="2">
-        <v>37287</v>
+        <v>39113</v>
       </c>
       <c r="K71" s="2">
         <v>73050</v>
@@ -3997,7 +3997,7 @@
         </is>
       </c>
       <c r="B72">
-        <v>4185932</v>
+        <v>381591</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -4006,7 +4006,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Ischemic heart disease</t>
+          <t>Cerebrovascular disease</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4031,11 +4031,11 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>414545008</t>
+          <t>62914000</t>
         </is>
       </c>
       <c r="J72" s="2">
-        <v>38383</v>
+        <v>37287</v>
       </c>
       <c r="K72" s="2">
         <v>73050</v>
@@ -4048,7 +4048,7 @@
         </is>
       </c>
       <c r="B73">
-        <v>437453</v>
+        <v>4116071</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -4057,12 +4057,12 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Accident due to environmental factor</t>
+          <t>Carcinoma of breast</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Observation</t>
+          <t>Condition</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -4072,7 +4072,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>Disorder</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4082,7 +4082,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>217591008</t>
+          <t>254838004</t>
         </is>
       </c>
       <c r="J73" s="2">
@@ -4099,7 +4099,7 @@
         </is>
       </c>
       <c r="B74">
-        <v>4071063</v>
+        <v>435656</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -4108,7 +4108,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Sepsis of the newborn</t>
+          <t>Neonatal jaundice</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -4123,7 +4123,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Disorder</t>
+          <t>Clinical Finding</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -4133,11 +4133,11 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>206376005</t>
+          <t>387712008</t>
         </is>
       </c>
       <c r="J74" s="2">
-        <v>37287</v>
+        <v>37652</v>
       </c>
       <c r="K74" s="2">
         <v>73050</v>
@@ -4150,7 +4150,7 @@
         </is>
       </c>
       <c r="B75">
-        <v>439237</v>
+        <v>4244495</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -4159,12 +4159,12 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>Carcinoma in situ of gastrointestinal tract</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Observation</t>
+          <t>Condition</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -4174,7 +4174,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>Disorder</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -4184,7 +4184,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>52684005</t>
+          <t>92600008</t>
         </is>
       </c>
       <c r="J75" s="2">
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="B76">
-        <v>255573</v>
+        <v>442013</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -4210,7 +4210,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Chronic obstructive pulmonary disease</t>
+          <t>Burn</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -4235,7 +4235,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>13645005</t>
+          <t>125666000</t>
         </is>
       </c>
       <c r="J76" s="2">
@@ -4252,7 +4252,7 @@
         </is>
       </c>
       <c r="B77">
-        <v>437611</v>
+        <v>40492938</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -4261,7 +4261,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Ectopic pregnancy</t>
+          <t>Carcinoma of lung</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -4286,11 +4286,11 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>34801009</t>
+          <t>448993007</t>
         </is>
       </c>
       <c r="J77" s="2">
-        <v>37287</v>
+        <v>40755</v>
       </c>
       <c r="K77" s="2">
         <v>73050</v>
@@ -4303,7 +4303,7 @@
         </is>
       </c>
       <c r="B78">
-        <v>81251</v>
+        <v>4291005</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Neoplasm of breast</t>
+          <t>Viral hepatitis</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -4337,7 +4337,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>126926005</t>
+          <t>3738000</t>
         </is>
       </c>
       <c r="J78" s="2">
@@ -4354,7 +4354,7 @@
         </is>
       </c>
       <c r="B79">
-        <v>4130986</v>
+        <v>133024</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Neoplasm of mouth</t>
+          <t>Tetanus neonatorum</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -4388,7 +4388,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>126797001</t>
+          <t>43424001</t>
         </is>
       </c>
       <c r="J79" s="2">
@@ -4405,7 +4405,7 @@
         </is>
       </c>
       <c r="B80">
-        <v>4155221</v>
+        <v>134057</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -4414,12 +4414,12 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Exposure to poison of venomous animals and plants</t>
+          <t>Disorder of cardiovascular system</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Observation</t>
+          <t>Condition</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -4429,7 +4429,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>Disorder</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -4439,7 +4439,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>269705003</t>
+          <t>49601007</t>
         </is>
       </c>
       <c r="J80" s="2">
@@ -4456,7 +4456,7 @@
         </is>
       </c>
       <c r="B81">
-        <v>443783</v>
+        <v>4101415</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -4465,12 +4465,12 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Chronic disease</t>
+          <t>Homicide</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Condition</t>
+          <t>Observation</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -4480,7 +4480,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Disorder</t>
+          <t>Event</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -4490,7 +4490,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>27624003</t>
+          <t>27935005</t>
         </is>
       </c>
       <c r="J81" s="2">
@@ -4507,7 +4507,7 @@
         </is>
       </c>
       <c r="B82">
-        <v>4143700</v>
+        <v>45877493</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -4516,22 +4516,22 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Smoke inhalation injury</t>
+          <t>Animal bite</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Condition</t>
+          <t>Meas Value</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>SNOMED</t>
+          <t>LOINC</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Disorder</t>
+          <t>Answer</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -4541,11 +4541,11 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>426936004</t>
+          <t>LA17118-3</t>
         </is>
       </c>
       <c r="J82" s="2">
-        <v>39294</v>
+        <v>25569</v>
       </c>
       <c r="K82" s="2">
         <v>73050</v>
@@ -4558,7 +4558,7 @@
         </is>
       </c>
       <c r="B83">
-        <v>435713</v>
+        <v>434557</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -4567,12 +4567,12 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Transport accident</t>
+          <t>Tuberculosis</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Observation</t>
+          <t>Condition</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>Disorder</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -4592,7 +4592,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>274215009</t>
+          <t>56717001</t>
         </is>
       </c>
       <c r="J83" s="2">
@@ -4609,7 +4609,7 @@
         </is>
       </c>
       <c r="B84">
-        <v>193827</v>
+        <v>200763</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -4618,7 +4618,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Obstructed labor</t>
+          <t>Chronic hepatitis</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -4643,7 +4643,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>199746004</t>
+          <t>76783007</t>
         </is>
       </c>
       <c r="J84" s="2">
@@ -4660,7 +4660,7 @@
         </is>
       </c>
       <c r="B85">
-        <v>37175321</v>
+        <v>4185932</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Antepartum septicemia</t>
+          <t>Ischemic heart disease</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -4694,11 +4694,11 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>137701000119106</t>
+          <t>414545008</t>
         </is>
       </c>
       <c r="J85" s="2">
-        <v>45107</v>
+        <v>38383</v>
       </c>
       <c r="K85" s="2">
         <v>73050</v>
@@ -4711,7 +4711,7 @@
         </is>
       </c>
       <c r="B86">
-        <v>4030555</v>
+        <v>437611</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Measles</t>
+          <t>Ectopic pregnancy</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -4745,7 +4745,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>14189004</t>
+          <t>34801009</t>
         </is>
       </c>
       <c r="J86" s="2">
@@ -4762,7 +4762,7 @@
         </is>
       </c>
       <c r="B87">
-        <v>257778</v>
+        <v>435713</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -4771,12 +4771,12 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Pertussis</t>
+          <t>Transport accident</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Condition</t>
+          <t>Observation</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -4786,7 +4786,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Disorder</t>
+          <t>Event</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -4796,7 +4796,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>27836007</t>
+          <t>274215009</t>
         </is>
       </c>
       <c r="J87" s="2">
@@ -4813,7 +4813,7 @@
         </is>
       </c>
       <c r="B88">
-        <v>4099889</v>
+        <v>193827</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -4822,7 +4822,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Anemia of pregnancy</t>
+          <t>Obstructed labor</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -4847,7 +4847,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>27342004</t>
+          <t>199746004</t>
         </is>
       </c>
       <c r="J88" s="2">
@@ -4864,7 +4864,7 @@
         </is>
       </c>
       <c r="B89">
-        <v>444066</v>
+        <v>4030555</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -4873,7 +4873,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Rupture of uterus</t>
+          <t>Measles</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -4898,7 +4898,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>34430009</t>
+          <t>14189004</t>
         </is>
       </c>
       <c r="J89" s="2">
@@ -4915,7 +4915,7 @@
         </is>
       </c>
       <c r="B90">
-        <v>440022</v>
+        <v>257778</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -4924,7 +4924,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Dengue</t>
+          <t>Pertussis</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -4949,7 +4949,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>38362002</t>
+          <t>27836007</t>
         </is>
       </c>
       <c r="J90" s="2">
@@ -5323,7 +5323,7 @@
         </is>
       </c>
       <c r="B98">
-        <v>4071848</v>
+        <v>4072113</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -5332,7 +5332,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Malawi</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -5357,7 +5357,7 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>223567001</t>
+          <t>223540007</t>
         </is>
       </c>
       <c r="J98" s="2">
@@ -5374,7 +5374,7 @@
         </is>
       </c>
       <c r="B99">
-        <v>4075209</v>
+        <v>4071848</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Burkina Faso</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -5408,7 +5408,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>223554004</t>
+          <t>223567001</t>
         </is>
       </c>
       <c r="J99" s="2">
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="B100">
-        <v>4075204</v>
+        <v>4075209</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -5434,7 +5434,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Burkina Faso</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -5459,7 +5459,7 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>223534000</t>
+          <t>223554004</t>
         </is>
       </c>
       <c r="J100" s="2">
@@ -5476,7 +5476,7 @@
         </is>
       </c>
       <c r="B101">
-        <v>4072113</v>
+        <v>4075204</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -5485,7 +5485,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Malawi</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -5510,7 +5510,7 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>223540007</t>
+          <t>223534000</t>
         </is>
       </c>
       <c r="J101" s="2">
@@ -5731,7 +5731,7 @@
         </is>
       </c>
       <c r="B106">
-        <v>45881961</v>
+        <v>45881960</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>65 years old or older</t>
+          <t>40 - 64 years old</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -5765,7 +5765,7 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>LA14240-8</t>
+          <t>LA14239-0</t>
         </is>
       </c>
       <c r="J106" s="2">
@@ -5962,11 +5962,11 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>value_as_concept_id</t>
+          <t>observation_concept_id</t>
         </is>
       </c>
       <c r="B111">
-        <v>45883427</v>
+        <v>42528763</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -5975,12 +5975,12 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>5 - 14 years old</t>
+          <t>Highest level of education</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Meas Value</t>
+          <t>Observation</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -5990,7 +5990,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Answer</t>
+          <t>Clinical Observation</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -6000,11 +6000,11 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>LA14236-6</t>
+          <t>82589-3</t>
         </is>
       </c>
       <c r="J111" s="2">
-        <v>25569</v>
+        <v>42787</v>
       </c>
       <c r="K111" s="2">
         <v>73050</v>
@@ -6017,7 +6017,7 @@
         </is>
       </c>
       <c r="B112">
-        <v>45881960</v>
+        <v>44800023</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -6026,22 +6026,22 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>40 - 64 years old</t>
+          <t>Educated to primary school level</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Meas Value</t>
+          <t>Observation</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>LOINC</t>
+          <t>SNOMED</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Answer</t>
+          <t>Clinical Finding</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -6051,11 +6051,11 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>LA14239-0</t>
+          <t>342271000000107</t>
         </is>
       </c>
       <c r="J112" s="2">
-        <v>25569</v>
+        <v>39722</v>
       </c>
       <c r="K112" s="2">
         <v>73050</v>
@@ -6068,7 +6068,7 @@
         </is>
       </c>
       <c r="B113">
-        <v>45884506</v>
+        <v>45881961</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -6077,7 +6077,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Under 5 Years Old</t>
+          <t>65 years old or older</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -6102,7 +6102,7 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>LA14235-8</t>
+          <t>LA14240-8</t>
         </is>
       </c>
       <c r="J113" s="2">
@@ -6119,7 +6119,7 @@
         </is>
       </c>
       <c r="B114">
-        <v>45876531</v>
+        <v>43021808</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -6128,22 +6128,22 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>15 - 24 years old</t>
+          <t>Educated to high school level</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Meas Value</t>
+          <t>Observation</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>LOINC</t>
+          <t>SNOMED</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Answer</t>
+          <t>Clinical Finding</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -6153,11 +6153,11 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>LA14237-4</t>
+          <t>473461003</t>
         </is>
       </c>
       <c r="J114" s="2">
-        <v>25569</v>
+        <v>41305</v>
       </c>
       <c r="K114" s="2">
         <v>73050</v>
@@ -6166,11 +6166,11 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>value_as_concept_id</t>
+          <t>observation_concept_id</t>
         </is>
       </c>
       <c r="B115">
-        <v>45883482</v>
+        <v>4249447</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -6179,36 +6179,31 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>25 - 39 years old</t>
+          <t>Economic status</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Meas Value</t>
+          <t>Observation</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>LOINC</t>
+          <t>SNOMED</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Answer</t>
-        </is>
-      </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>S</t>
+          <t>Social Context</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>LA14238-2</t>
+          <t>73831000</t>
         </is>
       </c>
       <c r="J115" s="2">
-        <v>25569</v>
+        <v>37287</v>
       </c>
       <c r="K115" s="2">
         <v>73050</v>
@@ -6217,11 +6212,11 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>observation_concept_id</t>
+          <t>value_as_concept_id</t>
         </is>
       </c>
       <c r="B116">
-        <v>42528763</v>
+        <v>4198183</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -6230,7 +6225,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Highest level of education</t>
+          <t>Lower middle class economic status</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -6240,26 +6235,21 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>LOINC</t>
+          <t>SNOMED</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Clinical Observation</t>
-        </is>
-      </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>S</t>
+          <t>Social Context</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>82589-3</t>
+          <t>80123004</t>
         </is>
       </c>
       <c r="J116" s="2">
-        <v>42787</v>
+        <v>37287</v>
       </c>
       <c r="K116" s="2">
         <v>73050</v>
@@ -6272,7 +6262,7 @@
         </is>
       </c>
       <c r="B117">
-        <v>44800023</v>
+        <v>4330874</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -6281,7 +6271,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Educated to primary school level</t>
+          <t>Middle class economic status</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -6296,21 +6286,16 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Clinical Finding</t>
-        </is>
-      </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>S</t>
+          <t>Social Context</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>342271000000107</t>
+          <t>22575004</t>
         </is>
       </c>
       <c r="J117" s="2">
-        <v>39722</v>
+        <v>37287</v>
       </c>
       <c r="K117" s="2">
         <v>73050</v>
@@ -6323,7 +6308,7 @@
         </is>
       </c>
       <c r="B118">
-        <v>43021808</v>
+        <v>4277050</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -6332,7 +6317,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Educated to high school level</t>
+          <t>Lower class economic status</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -6347,21 +6332,16 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Clinical Finding</t>
-        </is>
-      </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>S</t>
+          <t>Social Context</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>473461003</t>
+          <t>36877009</t>
         </is>
       </c>
       <c r="J118" s="2">
-        <v>41305</v>
+        <v>37287</v>
       </c>
       <c r="K118" s="2">
         <v>73050</v>
@@ -6370,11 +6350,11 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>observation_concept_id</t>
+          <t>value_as_concept_id</t>
         </is>
       </c>
       <c r="B119">
-        <v>4249447</v>
+        <v>45880050</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -6383,31 +6363,36 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Economic status</t>
+          <t>No schooling</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Observation</t>
+          <t>Meas Value</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>SNOMED</t>
+          <t>LOINC</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Social Context</t>
+          <t>Answer</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>S</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>73831000</t>
+          <t>LA35-1</t>
         </is>
       </c>
       <c r="J119" s="2">
-        <v>37287</v>
+        <v>25569</v>
       </c>
       <c r="K119" s="2">
         <v>73050</v>
@@ -6420,7 +6405,7 @@
         </is>
       </c>
       <c r="B120">
-        <v>4198183</v>
+        <v>45883482</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -6429,31 +6414,36 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Lower middle class economic status</t>
+          <t>25 - 39 years old</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Observation</t>
+          <t>Meas Value</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>SNOMED</t>
+          <t>LOINC</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Social Context</t>
+          <t>Answer</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>S</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>80123004</t>
+          <t>LA14238-2</t>
         </is>
       </c>
       <c r="J120" s="2">
-        <v>37287</v>
+        <v>25569</v>
       </c>
       <c r="K120" s="2">
         <v>73050</v>
@@ -6466,7 +6456,7 @@
         </is>
       </c>
       <c r="B121">
-        <v>4330874</v>
+        <v>4059166</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -6475,7 +6465,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Middle class economic status</t>
+          <t>Higher education</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -6490,12 +6480,17 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Social Context</t>
+          <t>Clinical Finding</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>S</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>22575004</t>
+          <t>161122005</t>
         </is>
       </c>
       <c r="J121" s="2">
@@ -6512,7 +6507,7 @@
         </is>
       </c>
       <c r="B122">
-        <v>4277050</v>
+        <v>4311552</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -6521,7 +6516,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Lower class economic status</t>
+          <t>Upper class economic status</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -6541,7 +6536,7 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>36877009</t>
+          <t>85483007</t>
         </is>
       </c>
       <c r="J122" s="2">
@@ -6558,7 +6553,7 @@
         </is>
       </c>
       <c r="B123">
-        <v>45880050</v>
+        <v>4274784</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -6567,36 +6562,31 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>No schooling</t>
+          <t>Upper middle class economic status</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Meas Value</t>
+          <t>Observation</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>LOINC</t>
+          <t>SNOMED</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Answer</t>
-        </is>
-      </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>S</t>
+          <t>Social Context</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>LA35-1</t>
+          <t>64816001</t>
         </is>
       </c>
       <c r="J123" s="2">
-        <v>25569</v>
+        <v>37287</v>
       </c>
       <c r="K123" s="2">
         <v>73050</v>
@@ -6609,7 +6599,7 @@
         </is>
       </c>
       <c r="B124">
-        <v>4059166</v>
+        <v>45876531</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -6618,22 +6608,22 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Higher education</t>
+          <t>15 - 24 years old</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Observation</t>
+          <t>Meas Value</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>SNOMED</t>
+          <t>LOINC</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Clinical Finding</t>
+          <t>Answer</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -6643,11 +6633,11 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>161122005</t>
+          <t>LA14237-4</t>
         </is>
       </c>
       <c r="J124" s="2">
-        <v>37287</v>
+        <v>25569</v>
       </c>
       <c r="K124" s="2">
         <v>73050</v>
@@ -6660,7 +6650,7 @@
         </is>
       </c>
       <c r="B125">
-        <v>4311552</v>
+        <v>45883427</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -6669,31 +6659,36 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Upper class economic status</t>
+          <t>5 - 14 years old</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Observation</t>
+          <t>Meas Value</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>SNOMED</t>
+          <t>LOINC</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Social Context</t>
+          <t>Answer</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>S</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>85483007</t>
+          <t>LA14236-6</t>
         </is>
       </c>
       <c r="J125" s="2">
-        <v>37287</v>
+        <v>25569</v>
       </c>
       <c r="K125" s="2">
         <v>73050</v>
@@ -6706,7 +6701,7 @@
         </is>
       </c>
       <c r="B126">
-        <v>4274784</v>
+        <v>45884506</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -6715,31 +6710,36 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Upper middle class economic status</t>
+          <t>Under 5 Years Old</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Observation</t>
+          <t>Meas Value</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>SNOMED</t>
+          <t>LOINC</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Social Context</t>
+          <t>Answer</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>S</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>64816001</t>
+          <t>LA14235-8</t>
         </is>
       </c>
       <c r="J126" s="2">
-        <v>37287</v>
+        <v>25569</v>
       </c>
       <c r="K126" s="2">
         <v>73050</v>
